--- a/TestData/TestData.xlsx
+++ b/TestData/TestData.xlsx
@@ -27,7 +27,7 @@
     <t>Kuchbhi@123</t>
   </si>
   <si>
-    <t>SONY</t>
+    <t>VIJAY</t>
   </si>
 </sst>
 </file>
